--- a/Outputs/Scenarios/PtX_demand_LU_Methanol.xlsx
+++ b/Outputs/Scenarios/PtX_demand_LU_Methanol.xlsx
@@ -1037,7 +1037,7 @@
         <v>3.274988082656695e-05</v>
       </c>
       <c r="K16" t="n">
-        <v>7.434125339417839e-06</v>
+        <v>1.734629245864163e-05</v>
       </c>
     </row>
     <row r="17">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>1.239020889902973e-05</v>
+        <v>5.203887737592489e-06</v>
       </c>
     </row>
     <row r="19">
@@ -1370,7 +1370,7 @@
         <v>1.588659768611818e-05</v>
       </c>
       <c r="K25" t="n">
-        <v>9.743020561730945e-05</v>
+        <v>9.743020561730947e-05</v>
       </c>
     </row>
     <row r="26">
@@ -1481,7 +1481,7 @@
         <v>4.718703464600818e-07</v>
       </c>
       <c r="K28" t="n">
-        <v>4.956083559611892e-06</v>
+        <v>2.230237601825352e-06</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>4.848221138366855e-05</v>
       </c>
       <c r="K30" t="n">
-        <v>3.722037350691854e-05</v>
+        <v>8.684753818280995e-05</v>
       </c>
     </row>
     <row r="31">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>6.203395584486424e-05</v>
+        <v>2.605426145484299e-05</v>
       </c>
     </row>
     <row r="33">
@@ -1999,7 +1999,7 @@
         <v>2.551695335982555e-06</v>
       </c>
       <c r="K42" t="n">
-        <v>2.48135823379457e-05</v>
+        <v>1.116611205207557e-05</v>
       </c>
     </row>
     <row r="43">
